--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,13 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,15 +784,15 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="D4" s="11" t="n">
+        <v>585.3</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -816,19 +813,19 @@
       <c r="L4" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>29.5</v>
+      <c r="N4" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -838,13 +835,13 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>18.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -864,76 +861,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>19.1</v>
+        <v>388.3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L5" s="15" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q5" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>17.6</v>
+        <v>13</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
+        <v>13.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -949,76 +946,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.5</v>
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.1</v>
+        <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.1</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.5</v>
+        <v>18.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.4</v>
+        <v>512.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27</v>
+        <v>17.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1034,76 +1031,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.5</v>
+        <v>229.6</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>98</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.8</v>
+        <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>52.4</v>
+        <v>22.9</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.1</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V7" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>16.6</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.5</v>
+        <v>19</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1119,76 +1116,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>17.6</v>
+        <v>2224.9</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>50.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>63.1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.9</v>
+        <v>706.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.8</v>
+        <v>260.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>14.1</v>
+        <v>51.1</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>60.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40.3</v>
+        <v>166.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.6</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>11.4</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,75 +1201,77 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1118.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>93.09999999999999</v>
+        <v>445</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>30.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.1</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>706.4</v>
+        <v>229.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>0.2</v>
+      <c r="L9" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59</v>
+        <v>21.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>114</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>88.09999999999999</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q9" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.2</v>
+        <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>212.6</v>
+        <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="W9" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="W9" s="14" t="n">
         <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>117.8</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1287,74 +1286,76 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M10" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>15.8</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>99.8</v>
+        <v>15.3</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="Q10" s="14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q10" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="14" t="n">
         <v>17.6</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.6</v>
+        <v>62.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>83</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1372,17 +1373,17 @@
       <c r="C11" s="3" t="n">
         <v>191.8</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
@@ -1394,53 +1395,43 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M11" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q11" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>1.1</v>
+      <c r="Q11" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>17.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>140649.1</v>
+        <v>22.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>717.5</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>80494</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="11" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1457,19 +1448,19 @@
       <c r="C12" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1481,40 +1472,40 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="12" t="n">
         <v>14.3</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>83.90000000000001</v>
+      <c r="M12" s="12" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>931.8</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="15" t="n">
+      <c r="V12" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="W12" s="13" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>12.3</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1538,20 +1529,20 @@
       <c r="C13" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1562,38 +1553,38 @@
       <c r="K13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.9</v>
+        <v>74.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>14.8</v>
@@ -1623,13 +1614,13 @@
       <c r="C14" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1639,58 +1630,58 @@
         <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="L14" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1708,49 +1699,49 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1760,7 +1751,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1791,40 +1782,40 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1475.2</v>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="14" t="n">
         <v>674.7</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="F16" s="14" t="n">
+        <v>92.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>164.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L16" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="14" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1140.4</v>
+        <v>712.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.5</v>
@@ -1832,11 +1823,11 @@
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>83</v>
+      <c r="R16" s="14" t="n">
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1847,17 +1838,17 @@
       <c r="U16" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="14" t="n">
         <v>84.3</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="14" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1208.8</v>
+        <v>450.2</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1878,14 +1869,14 @@
       <c r="C17" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>8.800000000000001</v>
+      <c r="D17" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>18.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1897,30 +1888,30 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>19.1</v>
+      <c r="M17" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>11.8</v>
+        <v>15.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1930,19 +1921,19 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V17" s="10" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="V17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>15.3</v>
@@ -1961,25 +1952,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="E18" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>48.4</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1987,10 +1978,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -2000,10 +1991,10 @@
         <v>91</v>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2015,14 +2006,14 @@
       <c r="U18" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="X18" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>84</v>
@@ -2046,17 +2037,17 @@
       <c r="C19" s="3" t="n">
         <v>440.6</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>14</v>
+      <c r="G19" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2070,25 +2061,25 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="15" t="n">
-        <v>1.4</v>
+      <c r="M19" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R19" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R19" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2100,11 +2091,11 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>87</v>
+      <c r="V19" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>18.3</v>
@@ -2113,7 +2104,7 @@
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>17.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2131,49 +2122,49 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E20" s="11" t="n">
+      <c r="D20" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.8</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M20" s="15" t="n">
+      <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2183,12 +2174,12 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V20" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V20" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2216,49 +2207,49 @@
       <c r="C21" s="3" t="n">
         <v>261.7</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>11.7</v>
+        <v>16.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R21" s="11" t="n">
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R21" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2270,10 +2261,10 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2299,43 +2290,43 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="11" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>1.4</v>
+      <c r="L22" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.1</v>
+        <v>16.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2343,7 +2334,7 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2355,10 +2346,10 @@
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2368,7 +2359,7 @@
         <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2386,33 +2377,33 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>91.8</v>
+      <c r="E23" s="12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>91.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>94.3</v>
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>12.2</v>
+      <c r="L23" s="14" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>72.2</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>30.4</v>
@@ -2423,14 +2414,14 @@
       <c r="P23" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="14" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="12" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2438,17 +2429,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="11" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="W23" s="10" t="n">
+      <c r="V23" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>929.5</v>
+        <v>435.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2467,15 +2458,15 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2491,27 +2482,27 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="14" t="n">
         <v>15.2</v>
       </c>
-      <c r="M24" s="10" t="n">
-        <v>43.4</v>
+      <c r="M24" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>221.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="14" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2523,10 +2514,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2552,16 +2543,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>18.8</v>
+      <c r="E25" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9</v>
@@ -2575,30 +2566,30 @@
       <c r="J25" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="12" t="n">
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>84.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.5</v>
+        <v>15.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>91.5</v>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
+      <c r="Q25" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R25" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2606,10 +2597,10 @@
       <c r="U25" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,22 +2626,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>326</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2658,17 +2649,17 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>1.4</v>
+      <c r="K26" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2676,11 +2667,11 @@
       <c r="P26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="R26" s="12" t="n">
+        <v>17.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2691,20 +2682,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="12" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2720,38 +2711,38 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>287.8</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2759,25 +2750,25 @@
       <c r="P27" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R27" s="3" t="n">
+      <c r="Q27" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2803,22 +2794,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>82.8</v>
+        <v>13.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2826,17 +2817,17 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2844,10 +2835,10 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2859,20 +2850,20 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2890,38 +2881,38 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="D29" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="8" t="n">
+      <c r="K29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.1</v>
+        <v>21.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2929,29 +2920,29 @@
       <c r="P29" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
         <v>21.7</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>82.09999999999999</v>
+      <c r="X29" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2975,34 +2966,34 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>1129.8</v>
-      </c>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="10" t="n">
+      <c r="D30" s="14" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="14" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="10" t="n">
-        <v>11.7</v>
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="12" t="n">
+        <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.9</v>
+        <v>79.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3010,29 +3001,29 @@
       <c r="P30" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="12" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="12" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561</v>
+        <v>361.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="W30" s="11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>441</v>
@@ -3056,13 +3047,13 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3079,47 +3070,47 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="10" t="n">
-        <v>14.7</v>
+      <c r="M31" s="12" t="n">
+        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>181.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>29.3</v>
+        <v>72.3</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V31" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>119.2</v>
+        <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>214.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3135,17 +3126,19 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3156,17 +3149,17 @@
       <c r="J32" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="12" t="n">
         <v>12.7</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M32" s="15" t="n">
+      <c r="L32" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>12.8</v>
+      <c r="N32" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3174,35 +3167,35 @@
       <c r="P32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>18.8</v>
+      <c r="R32" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V32" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V32" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3220,20 +3213,20 @@
       <c r="C33" s="3" t="n">
         <v>1482.8</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
+      <c r="D33" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E33" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>19.5</v>
+      <c r="F33" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>82.59999999999999</v>
+      <c r="H33" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3241,50 +3234,50 @@
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="L33" s="3" t="n">
+      <c r="K33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>84.8</v>
+      <c r="N33" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3305,38 +3298,38 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <v>11.5</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>109.5</v>
+      <c r="H34" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3344,11 +3337,11 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>17.8</v>
+      <c r="R34" s="12" t="n">
+        <v>17.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3359,17 +3352,17 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>12.8</v>
+      <c r="W34" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3386,19 +3379,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9492.799999999999</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="12" t="n">
         <v>19.3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>279.3</v>
@@ -3409,50 +3402,50 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.8</v>
+        <v>17.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>910</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="15" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V35" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V35" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>82.8</v>
+      <c r="W35" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>125.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3471,19 +3464,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9498.9</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G36" s="8" t="n">
-        <v>410.3</v>
+      <c r="G36" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
@@ -3494,17 +3487,17 @@
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="15" t="n">
-        <v>86.59999999999999</v>
+      <c r="L36" s="12" t="n">
+        <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>17.4</v>
+      <c r="N36" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3512,35 +3505,35 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="15" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R36" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V36" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>66.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3558,13 +3551,13 @@
       <c r="C37" s="3" t="n">
         <v>2192.8</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="14" t="n">
         <v>119.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="14" t="n">
         <v>665.7</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="14" t="n">
         <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3572,34 +3565,32 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>110.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L37" s="10" t="n">
+      <c r="K37" s="12" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>75.7</v>
       </c>
-      <c r="M37" s="10" t="n">
-        <v>711.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
+      <c r="M37" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>4420.3</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="12" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>81</v>
+      <c r="R37" s="12" t="n">
+        <v>87</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>84.8</v>
@@ -3608,19 +3599,19 @@
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="V37" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="12" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.8</v>
+        <v>409.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3639,38 +3630,38 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E38" s="11" t="n">
+        <v>438.6</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>18.9</v>
+      <c r="F38" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="14" t="n">
         <v>151.3</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="14" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>15.2</v>
@@ -3678,25 +3669,25 @@
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="12" t="n">
         <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3722,16 +3713,16 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39595.3</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>18.6</v>
+        <v>595.3</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>18.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>11.5</v>
@@ -3740,16 +3731,16 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3761,14 +3752,14 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>20.9</v>
+      <c r="S39" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
@@ -3776,11 +3767,11 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="13" t="inlineStr"/>
-      <c r="W39" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
+      <c r="V39" s="11" t="inlineStr"/>
+      <c r="W39" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3805,17 +3796,17 @@
       <c r="C40" s="3" t="n">
         <v>545.4</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3826,17 +3817,17 @@
       <c r="J40" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>0.8</v>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>19</v>
+      <c r="M40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3844,17 +3835,17 @@
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
@@ -3862,17 +3853,17 @@
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="12" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>408.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3888,37 +3879,37 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F41" s="11" t="n">
+      <c r="E41" s="12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>19.2</v>
@@ -3929,17 +3920,17 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>18</v>
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.6</v>
@@ -3947,17 +3938,17 @@
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>12</v>
+      <c r="W41" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>113.8</v>
+        <v>82</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3973,22 +3964,22 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E42" s="11" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
         <v>14.1</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
@@ -3996,28 +3987,28 @@
       <c r="J42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>0.9</v>
+      <c r="K42" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>15.1</v>
+        <v>22.6</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.1</v>
+        <v>19.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4030,19 +4021,19 @@
         <v>10.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>12.1</v>
+        <v>18.2</v>
+      </c>
+      <c r="W42" s="12" t="n">
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>110.1</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>58</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4058,76 +4049,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>18.1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>99.59999999999999</v>
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>35.4</v>
+        <v>16.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.9</v>
+        <v>16.2</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V43" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>22.6</v>
+        <v>58</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W43" s="12" t="n">
+        <v>15.2</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>557.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4143,76 +4134,74 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>10.5</v>
+        <v>237.1</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>18</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>62</v>
+        <v>10.8</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R44" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="V44" s="15" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="W44" s="15" t="n">
-        <v>95.5</v>
+      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="12" t="n">
+        <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>466.8</v>
+        <v>13.6</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>28.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4228,76 +4217,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>18.5</v>
+        <v>2983</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>797.1</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>10.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.3</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.8</v>
+        <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K45" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="14" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="M45" s="10" t="n">
-        <v>0.6</v>
+      <c r="M45" s="14" t="n">
+        <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.2</v>
+        <v>91.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>10.1</v>
+        <v>540.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>922.8</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>17.1</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q45" s="14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>102.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>58.5</v>
+        <v>351</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
-        <v>118.6</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>15.9</v>
+        <v>69</v>
+      </c>
+      <c r="V45" s="14" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="W45" s="14" t="n">
+        <v>22.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>82.8</v>
+        <v>466.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>44.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4315,23 +4304,23 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>0.1</v>
+      <c r="D46" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>145.9</v>
+        <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
@@ -4339,14 +4328,14 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>12</v>
+      <c r="M46" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>90.09999999999999</v>
@@ -4354,35 +4343,35 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R46" s="10" t="n">
-        <v>1.8</v>
+      <c r="Q46" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1414</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>11151.1</v>
+        <v>11.5</v>
+      </c>
+      <c r="V46" s="14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="12" t="n">
+        <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
